--- a/artfynd/A 36422-2021 artfynd.xlsx
+++ b/artfynd/A 36422-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36422-2021 artfynd.xlsx
+++ b/artfynd/A 36422-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112206846</v>
+        <v>112206831</v>
       </c>
       <c r="B2" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -756,6 +751,11 @@
           <t>2023-09-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Örtrikt dråg i granskog</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,19 +780,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112206831</v>
+        <v>112395257</v>
       </c>
       <c r="B3" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -814,19 +809,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr Masetjärnet, Vrm</t>
+          <t>Påterud, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333038</v>
+        <v>333022</v>
       </c>
       <c r="R3" t="n">
-        <v>6626637</v>
+        <v>6626626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,11 +853,6 @@
           <t>2023-09-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Örtrikt dråg i granskog</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,27 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Gran, Jan Rees</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112206837</v>
+        <v>112395258</v>
       </c>
       <c r="B4" t="n">
-        <v>90871</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4368</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr Masetjärnet, Vrm</t>
+          <t>Påterud, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333038</v>
+        <v>333033</v>
       </c>
       <c r="R4" t="n">
-        <v>6626637</v>
+        <v>6626617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,49 +962,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Gran, Jan Rees</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112395257</v>
+        <v>112395256</v>
       </c>
       <c r="B5" t="n">
-        <v>90916</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>788</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333022</v>
+        <v>333013</v>
       </c>
       <c r="R5" t="n">
-        <v>6626625</v>
+        <v>6626632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,15 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112395259</v>
+        <v>112206846</v>
       </c>
       <c r="B6" t="n">
-        <v>90906</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,16 +1100,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Påterud, Vrm</t>
+          <t>Norr Masetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333042</v>
+        <v>333038</v>
       </c>
       <c r="R6" t="n">
-        <v>6626628</v>
+        <v>6626637</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,27 +1159,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Roger Gran, Jan Rees</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112395260</v>
+        <v>112395259</v>
       </c>
       <c r="B7" t="n">
-        <v>90932</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>333038</v>
+        <v>333042</v>
       </c>
       <c r="R7" t="n">
-        <v>6626631</v>
+        <v>6626628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,50 +1268,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112395256</v>
+        <v>112206837</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>4368</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Påterud, Vrm</t>
+          <t>Norr Masetjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>333013</v>
+        <v>333038</v>
       </c>
       <c r="R8" t="n">
-        <v>6626631</v>
+        <v>6626637</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,15 +1356,209 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Gran, Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112395260</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Påterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>333038</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626631</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Jan Rees</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Jan Rees</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112395254</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Påterud, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>333021</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6626690</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
